--- a/Accounting_Journals_URL_List.xlsx
+++ b/Accounting_Journals_URL_List.xlsx
@@ -934,11 +934,7 @@
           <t>0951-3574</t>
         </is>
       </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>1758-9037</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="n"/>
     </row>
     <row r="9" ht="13.5" customHeight="1">
       <c r="A9" s="1" t="n">
@@ -1811,12 +1807,12 @@
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>2380-2863</t>
+          <t>2380-2146</t>
         </is>
       </c>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>2380-2871</t>
+          <t>2380-2154</t>
         </is>
       </c>
     </row>
@@ -2254,11 +2250,7 @@
           <t>1475-1488</t>
         </is>
       </c>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>1879-5919</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="n"/>
     </row>
     <row r="33" ht="13.5" customHeight="1">
       <c r="A33" s="1" t="n">
@@ -2736,14 +2728,10 @@
           <t>No RSS</t>
         </is>
       </c>
-      <c r="J41" s="1" t="inlineStr">
-        <is>
-          <t>1558-7878</t>
-        </is>
-      </c>
+      <c r="J41" s="1" t="n"/>
       <c r="K41" s="1" t="inlineStr">
         <is>
-          <t>1558-7886</t>
+          <t>1530-9320</t>
         </is>
       </c>
     </row>
@@ -2796,11 +2784,7 @@
           <t>1030-9616</t>
         </is>
       </c>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>2056-3396</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="n"/>
     </row>
     <row r="43" ht="13.5" customHeight="1">
       <c r="A43" s="1" t="n">
@@ -2957,11 +2941,7 @@
           <t>1321-7348</t>
         </is>
       </c>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>1758-7751</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="n"/>
     </row>
     <row r="46" ht="13.5" customHeight="1">
       <c r="A46" s="1" t="n">
@@ -3118,11 +3098,7 @@
           <t>1936-1270</t>
         </is>
       </c>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>1936-1289</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="n"/>
     </row>
     <row r="49" ht="13.5" customHeight="1">
       <c r="A49" s="1" t="n">
@@ -3173,11 +3149,7 @@
           <t>1834-7649</t>
         </is>
       </c>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>1758-9754</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="n"/>
     </row>
     <row r="50" ht="13.5" customHeight="1">
       <c r="A50" s="1" t="n">
@@ -3490,14 +3462,10 @@
           <t>No RSS</t>
         </is>
       </c>
-      <c r="J55" s="1" t="inlineStr">
-        <is>
-          <t>2380-2146</t>
-        </is>
-      </c>
+      <c r="J55" s="1" t="n"/>
       <c r="K55" s="1" t="inlineStr">
         <is>
-          <t>2380-2154</t>
+          <t>2380-2138</t>
         </is>
       </c>
     </row>
@@ -3550,11 +3518,7 @@
           <t>1096-3367</t>
         </is>
       </c>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>2051-663X</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="n"/>
     </row>
     <row r="57" ht="13.5" customHeight="1">
       <c r="A57" s="1" t="n">
@@ -3870,11 +3834,7 @@
           <t>1572-3097</t>
         </is>
       </c>
-      <c r="K62" s="6" t="inlineStr">
-        <is>
-          <t>1875-692X</t>
-        </is>
-      </c>
+      <c r="K62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">

--- a/Accounting_Journals_URL_List.xlsx
+++ b/Accounting_Journals_URL_List.xlsx
@@ -2195,11 +2195,7 @@
           <t>0882-6110</t>
         </is>
       </c>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>1873-6254</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="n"/>
     </row>
     <row r="32" ht="13.5" customHeight="1">
       <c r="A32" s="1" t="n">
@@ -2680,7 +2676,7 @@
       </c>
       <c r="K40" s="1" t="inlineStr">
         <is>
-          <t>1758-7743</t>
+          <t>1758-7654</t>
         </is>
       </c>
     </row>
